--- a/07-Defects/API_Defect_Report.xlsx
+++ b/07-Defects/API_Defect_Report.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Server consistently returns HTTP 200 OK in response headers, while embedding the documented code inside JSON responseCode.</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>System should validate presence of required parameters and return responseCode: 400 with message 'Bad request, email or password parameter is missing in POST request.'</t>
+          <t>Retested in latest run: Server returns responseCode 400 Bad Request as expected. Verified &amp; Closed.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>System bypasses parameter validation and returns HTTP 200 with responseCode: 404 and message 'User not found!'</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>System should validate presence of mandatory email parameter and return responseCode: 400 with message 'Bad request, email parameter is missing in PUT request.'</t>
+          <t>Retested in latest run: Server returns responseCode 400 Bad Request as expected. Verified &amp; Closed.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>System skips parameter presence check and returns HTTP 200 with responseCode: 404 and message 'Account not found!'</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">

--- a/07-Defects/API_Defect_Report.xlsx
+++ b/07-Defects/API_Defect_Report.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
+          <t>Server consistently returns wire HTTP 200 OK for all endpoints including error/mutation calls; documented status codes (201, 400, 404, 405) are embedded inside JSON responseCode field.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Open</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Documented</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>Retested: Server returns responseCode 400 (Bad request, email or password parameter is missing in POST request.) as expected. Defect Verified and Closed.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
           <t>Closed</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>Retested: Server returns responseCode 400 (Bad request, email parameter is missing in PUT request.) as expected. Defect Verified and Closed.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>Closed</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
     </row>
